--- a/data/trans_orig/IP28_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100747</t>
+          <t>100494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116904</t>
+          <t>116476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218666</t>
+          <t>219342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240436</t>
+          <t>240715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247147</t>
+          <t>247143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246118</t>
+          <t>245624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>489619</t>
+          <t>488410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>496743</t>
+          <t>496569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121629</t>
+          <t>121534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126371</t>
+          <t>126373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132804</t>
+          <t>133476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138355</t>
+          <t>138356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257782</t>
+          <t>257169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264657</t>
+          <t>264035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184946</t>
+          <t>184970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190828</t>
+          <t>190813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196594</t>
+          <t>196804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204122</t>
+          <t>203972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>384790</t>
+          <t>383935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393736</t>
+          <t>394029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>655049</t>
+          <t>655994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>665664</t>
+          <t>665588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>700814</t>
+          <t>700823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>710926</t>
+          <t>710732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1360837</t>
+          <t>1360707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1374632</t>
+          <t>1374213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126657</t>
+          <t>127277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126286</t>
+          <t>126363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131133</t>
+          <t>131130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256246</t>
+          <t>255754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>262118</t>
+          <t>262127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206728</t>
+          <t>206947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237864</t>
+          <t>237500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447342</t>
+          <t>448037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453227</t>
+          <t>453224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138252</t>
+          <t>138725</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145769</t>
+          <t>145757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>141104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147051</t>
+          <t>146944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281876</t>
+          <t>283008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291457</t>
+          <t>291567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144316</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152909</t>
+          <t>153031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157111</t>
+          <t>156832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164645</t>
+          <t>164536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304734</t>
+          <t>304691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316230</t>
+          <t>315856</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17707</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>626303</t>
+          <t>626836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>638830</t>
+          <t>638084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>671509</t>
+          <t>671264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682523</t>
+          <t>682334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302059</t>
+          <t>1302003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1317979</t>
+          <t>1318615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183697</t>
+          <t>183653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>187809</t>
+          <t>187808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>220504</t>
+          <t>219881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>406262</t>
+          <t>406224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411579</t>
+          <t>411637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159783</t>
+          <t>160089</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>165719</t>
+          <t>165755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161957</t>
+          <t>162525</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167800</t>
+          <t>167806</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324056</t>
+          <t>324129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332780</t>
+          <t>332804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152352</t>
+          <t>152053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153103</t>
+          <t>153004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159645</t>
+          <t>159058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307909</t>
+          <t>307557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314956</t>
+          <t>314970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>621744</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>630026</t>
+          <t>630001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655961</t>
+          <t>655726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>664136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1280921</t>
+          <t>1280509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1292547</t>
+          <t>1292470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>829</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>320</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158473</t>
+          <t>158470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177855</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336334</t>
+          <t>336550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340974</t>
+          <t>340817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167520</t>
+          <t>167015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206948</t>
+          <t>207398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>377621</t>
+          <t>377472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383341</t>
+          <t>383358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258864</t>
+          <t>259487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>270193</t>
+          <t>270328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293281</t>
+          <t>293648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301603</t>
+          <t>301700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>556410</t>
+          <t>555554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>570140</t>
+          <t>569702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17119</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>645521</t>
+          <t>645772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>657450</t>
+          <t>657626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744770</t>
+          <t>745024</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754838</t>
+          <t>754818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395948</t>
+          <t>1395189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1410273</t>
+          <t>1410718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP28_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,102 +728,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4342</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4274</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119482</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>116939</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120121</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102897</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100494</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100433</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>103495</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>119482</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>116476</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>120121</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>336</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219342</t>
+          <t>219274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>120121</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>120121</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120121</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>103495</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>103495</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>103495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>120121</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>120121</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>120121</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4802</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2991</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7211</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7757</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4805</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>249070</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>245627</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>250429</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>244935</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>240715</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>247143</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>240169</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>247148</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,79%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>249070</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>245624</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>250429</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>488410</t>
+          <t>489161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>496569</t>
+          <t>496683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>250429</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>250429</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>250429</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>247926</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>247926</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>247926</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>250429</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>250429</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>250429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5737</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5543</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133282</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138354</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124985</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>121534</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126373</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>121194</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>126372</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136944</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>133476</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138356</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>257169</t>
+          <t>257864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264035</t>
+          <t>264639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139019</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139019</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139019</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127014</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127014</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127014</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139019</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139019</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9445</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3214</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7108</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2077</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9245</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14191</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>201311</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196604</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204107</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>188864</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>184970</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>190813</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>184941</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190810</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201311</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>196804</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>203972</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>581</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383935</t>
+          <t>385044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>394029</t>
+          <t>394080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192078</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192078</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192078</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2100,69 +2100,69 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14251</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14519</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14566</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4886</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14795</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>706808</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>701367</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>710939</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>661681</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>655994</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>665588</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>655947</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>665910</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>97,83%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>706808</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>700823</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>710732</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1360707</t>
+          <t>1361081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1374213</t>
+          <t>1374651</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>715618</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>715618</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>715618</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>670513</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>670513</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>670513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>715618</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>715618</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>715618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1445</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4370</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5405</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>129769</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>126462</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>131126</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130202</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>127277</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>126674</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>131647</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>129769</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>126363</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>131130</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>379</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255754</t>
+          <t>256164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>262127</t>
+          <t>262073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>131768</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>131768</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>131768</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131647</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131647</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131647</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>131768</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>131768</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>131768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1455</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5361</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>241406</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>238445</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>242861</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>210313</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>206947</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>206987</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>211069</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>241406</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>237500</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>242861</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>638</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>448037</t>
+          <t>447406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453224</t>
+          <t>453223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>242861</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>242861</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>242861</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>211069</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>211069</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>211069</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>242861</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>242861</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>242861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6729</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4805</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2089</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9121</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9714</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2665</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6595</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12537</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>145034</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140970</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>146971</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>143041</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138725</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>145757</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138132</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>145756</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>93,43%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>145034</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>141104</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>146944</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>412</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283008</t>
+          <t>282207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291567</t>
+          <t>291483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>147699</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>147699</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>147699</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>147846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>147846</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>147846</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>147699</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>147699</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>147699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,67 +3704,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>5300</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10055</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>6047</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2764</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10770</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2646</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11691</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2465</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10169</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161701</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>164488</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>149748</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>145025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153031</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>144104</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>153149</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,12%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161701</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>156832</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>164536</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304691</t>
+          <t>304531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>315856</t>
+          <t>316131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167001</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167001</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167001</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155795</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155795</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155795</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>167001</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167001</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>167001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6709</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18126</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19521</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7493</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>19592</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>18066</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33683</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677911</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>671204</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>682621</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>633305</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>626836</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>638084</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>626765</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>638864</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>677911</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>671264</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>682334</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302003</t>
+          <t>1301154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318615</t>
+          <t>1317776</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689330</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689330</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689330</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>646357</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>646357</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>646357</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>689330</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>689330</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>689330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>114685</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>121329</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>114685</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>114685</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>114685</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>114685</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>121329</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>121329</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>121329</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>114685</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>114685</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>114685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,74 +4960,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3903</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1751</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4720</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4728</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>223200</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>219963</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>223866</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>186622</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>183653</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>187808</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>183645</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>187809</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,07%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>223200</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>219881</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>223866</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>622</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>406224</t>
+          <t>406164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411637</t>
+          <t>411574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>188373</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>188373</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>188373</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2594</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6425</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3409</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6931</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2594</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165860</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162029</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167801</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>163611</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160089</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165755</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>159619</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>166259</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,96%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165860</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162525</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>167806</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324129</t>
+          <t>324017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332804</t>
+          <t>332703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168454</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168454</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168454</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>167020</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>167020</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>167020</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>168454</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>168454</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>168454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4447</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4279</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7388</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>156990</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152810</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>159069</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>155289</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>152053</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>152221</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>156500</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>156990</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>153004</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>159058</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>431</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307557</t>
+          <t>307686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>314970</t>
+          <t>314993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>160392</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>160392</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>160392</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>156500</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>156500</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>156500</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>160392</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>160392</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>160392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,97 +5994,97 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11530</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11189</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11453</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11672</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>13033</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6102,99 +6102,99 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>660737</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655868</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>663520</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>944</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>626850</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>622033</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>630001</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>621769</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>630109</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>660737</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>655726</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>664136</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1287587</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1280407</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1292611</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1287587</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1280509</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1292470</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
           <t>98,45%</t>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>633222</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>633222</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>633222</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60859</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>224</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>101986</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>101986</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>101986</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118369</t>
+          <t>101986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3818</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>829</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>155804</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>153097</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156915</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>159135</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>158470</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>145026</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>143486</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>180534</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>176357</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>181837</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>529</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>339670</t>
+          <t>300829</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336550</t>
+          <t>297835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340817</t>
+          <t>301946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156915</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156915</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156915</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181837</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181837</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181837</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341137</t>
+          <t>302432</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341137</t>
+          <t>302432</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341137</t>
+          <t>302432</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1579</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5092</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,22 +7325,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>198566</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>194623</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>170752</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167015</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171562</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>172317</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169463</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>173022</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>210911</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>207398</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>471</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>381664</t>
+          <t>370883</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>377472</t>
+          <t>366890</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>383358</t>
+          <t>372489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>171562</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>171562</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>171562</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384053</t>
+          <t>373148</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384053</t>
+          <t>373148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384053</t>
+          <t>373148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9538</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8568</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3939</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14780</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9707</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>285981</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>280805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>288926</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>265699</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>259487</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>270328</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>298784</t>
+          <t>246300</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293648</t>
+          <t>238270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301700</t>
+          <t>250949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>564484</t>
+          <t>532281</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>555554</t>
+          <t>523845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569702</t>
+          <t>538233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>290343</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>290343</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>290343</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>303355</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>303355</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>303355</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>577623</t>
+          <t>545680</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>577623</t>
+          <t>545680</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>577623</t>
+          <t>545680</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12623</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5014</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16868</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>684657</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693647</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>927</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>653098</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>645772</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>657626</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>751088</t>
+          <t>615732</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>745024</t>
+          <t>608216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754818</t>
+          <t>620721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1404186</t>
+          <t>1305978</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395189</t>
+          <t>1296709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1410718</t>
+          <t>1312388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>662640</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>662640</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>662640</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625966</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421181</t>
+          <t>1323246</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421181</t>
+          <t>1323246</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421181</t>
+          <t>1323246</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
